--- a/JsonConverter/ExcelFiles/Character.xlsx
+++ b/JsonConverter/ExcelFiles/Character.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\Vamsurlike\Vamsurlike\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{123BA438-6DDB-44D7-BF73-203BA782ACCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98157F53-E50E-4A3B-9BBD-A7A2FC11D2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28308" yWindow="2796" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1248" windowWidth="28284" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId1"/>
+    <sheet name="Character" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>Id</t>
   </si>
@@ -37,16 +37,6 @@
     <t>(name)</t>
   </si>
   <si>
-    <t>300001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>300002</t>
-  </si>
-  <si>
-    <t>300003</t>
-  </si>
-  <si>
     <t>Antonio</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -169,6 +159,28 @@
   <si>
     <t>P</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>267001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>267002</t>
+  </si>
+  <si>
+    <t>267003</t>
+  </si>
+  <si>
+    <t>267004</t>
+  </si>
+  <si>
+    <t>267005</t>
+  </si>
+  <si>
+    <t>267006</t>
+  </si>
+  <si>
+    <t>267007</t>
   </si>
 </sst>
 </file>
@@ -559,28 +571,28 @@
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="15.6" x14ac:dyDescent="0.35">
@@ -591,31 +603,31 @@
         <v>3</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J2" s="7" t="s">
         <v>3</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -626,48 +638,48 @@
         <v>2</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>8</v>
       </c>
       <c r="C4" s="11">
         <v>100</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5">
         <v>10</v>
@@ -679,30 +691,30 @@
         <v>0.1</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>6</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="11">
         <v>100</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F5" s="5">
         <v>5</v>
@@ -714,10 +726,10 @@
         <v>0.1</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K5" s="5">
         <v>10</v>
@@ -725,19 +737,19 @@
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="12" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>10</v>
       </c>
       <c r="C6" s="11">
         <v>100</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F6" s="5">
         <v>5</v>
@@ -749,17 +761,19 @@
         <v>0.1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K6" s="5">
         <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="9"/>
+      <c r="A7" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="B7" s="10"/>
       <c r="C7" s="11"/>
       <c r="D7" s="4"/>
@@ -772,7 +786,9 @@
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13"/>
+      <c r="A8" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="B8" s="14"/>
       <c r="C8" s="15"/>
       <c r="D8" s="4"/>
@@ -785,7 +801,9 @@
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="13"/>
+      <c r="A9" s="9" t="s">
+        <v>41</v>
+      </c>
       <c r="B9" s="14"/>
       <c r="C9" s="15"/>
       <c r="D9" s="4"/>
@@ -798,7 +816,9 @@
       <c r="K9" s="5"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="16"/>
+      <c r="A10" s="9" t="s">
+        <v>42</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="5"/>
       <c r="D10" s="4"/>
